--- a/Hexalevel_Financial_Management_Dashboard.xlsx
+++ b/Hexalevel_Financial_Management_Dashboard.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14445" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +15,7 @@
     <sheet name="Scenario C &amp; Net Profit" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -32,54 +33,54 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <i val="1"/>
-      <color rgb="FFD1FAE5"/>
+      <color rgb="00D1FAE5"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FF475569"/>
+      <color rgb="00475569"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FF1E293B"/>
+      <color rgb="001E293B"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FF065F46"/>
+      <color rgb="00065F46"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="FF1F2937"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FF1F2937"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -92,66 +93,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0D5C52"/>
-        <bgColor rgb="FF0D5C52"/>
+        <fgColor rgb="000D5C52"/>
+        <bgColor rgb="000D5C52"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2FE"/>
-        <bgColor rgb="FFE0F2FE"/>
+        <fgColor rgb="00E0F2FE"/>
+        <bgColor rgb="00E0F2FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0E7FF"/>
-        <bgColor rgb="FFE0E7FF"/>
+        <fgColor rgb="00E0E7FF"/>
+        <bgColor rgb="00E0E7FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9C3"/>
-        <bgColor rgb="FFFEF9C3"/>
+        <fgColor rgb="00FEF9C3"/>
+        <bgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE4E6"/>
-        <bgColor rgb="FFFFE4E6"/>
+        <fgColor rgb="00FFE4E6"/>
+        <bgColor rgb="00FFE4E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6F9ED"/>
-        <bgColor rgb="FFE6F9ED"/>
+        <fgColor rgb="00E6F9ED"/>
+        <bgColor rgb="00E6F9ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3E8FF"/>
-        <bgColor rgb="FFF3E8FF"/>
+        <fgColor rgb="00F3E8FF"/>
+        <bgColor rgb="00F3E8FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-        <bgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEDD5"/>
-        <bgColor rgb="FFFFEDD5"/>
+        <fgColor rgb="00FFEDD5"/>
+        <bgColor rgb="00FFEDD5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF093C35"/>
-        <bgColor rgb="FF093C35"/>
+        <fgColor rgb="00093C35"/>
+        <bgColor rgb="00093C35"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -161,128 +162,101 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD1D5DB"/>
+        <color rgb="00D1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="FFD1D5DB"/>
+        <color rgb="00D1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="FFD1D5DB"/>
+        <color rgb="00D1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD1D5DB"/>
+        <color rgb="00D1D5DB"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD1D5DB"/>
+        <color rgb="00D1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="FFD1D5DB"/>
+        <color rgb="00D1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="FF093C35"/>
+        <color rgb="00093C35"/>
       </top>
       <bottom style="double">
-        <color rgb="FF093C35"/>
+        <color rgb="00093C35"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD1D5DB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD1D5DB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF093C35"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF093C35"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF093C35"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF093C35"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF093C35"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF093C35"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -320,6 +294,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -329,84 +306,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -772,312 +674,318 @@
   <dimension ref="B2:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="20" min="1" max="1"/>
-    <col width="13" customWidth="1" style="20" min="2" max="4"/>
-    <col width="4" customWidth="1" style="20" min="5" max="5"/>
-    <col width="14" customWidth="1" style="20" min="6" max="8"/>
-    <col width="4" customWidth="1" style="20" min="9" max="9"/>
-    <col width="15" customWidth="1" style="20" min="10" max="11"/>
-    <col width="4" customWidth="1" style="20" min="12" max="12"/>
-    <col width="22" customWidth="1" style="20" min="13" max="13"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="2" ht="24" customHeight="1" s="20">
-      <c r="B2" s="19" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>HEXALEVEL — MONTHLY REVENUE DASHBOARD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="44" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>All values update automatically — add rows to Projects / Revenue Split / Expenses</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="20">
-      <c r="B5" s="37" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TOTAL REVENUE (PKR)</t>
         </is>
       </c>
-      <c r="C5" s="48" t="n"/>
-      <c r="D5" s="49" t="n"/>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>COMPANY SHARE (50%)</t>
         </is>
       </c>
-      <c r="G5" s="48" t="n"/>
-      <c r="H5" s="49" t="n"/>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>TEAM SHARE (50%)</t>
         </is>
       </c>
-      <c r="K5" s="49" t="n"/>
-      <c r="M5" s="41" t="inlineStr">
+      <c r="K5" s="8" t="n"/>
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>TOTAL PURCHASES</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.95" customHeight="1" s="20">
-      <c r="B6" s="21">
+    <row r="6" ht="28" customHeight="1">
+      <c r="B6" s="10">
         <f>'Revenue Split'!B24</f>
         <v/>
       </c>
-      <c r="C6" s="48" t="n"/>
-      <c r="D6" s="49" t="n"/>
-      <c r="F6" s="42">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="F6" s="11">
         <f>'Revenue Split'!C24</f>
         <v/>
       </c>
-      <c r="G6" s="48" t="n"/>
-      <c r="H6" s="49" t="n"/>
-      <c r="J6" s="32">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="J6" s="12">
         <f>'Revenue Split'!D24</f>
         <v/>
       </c>
-      <c r="K6" s="49" t="n"/>
-      <c r="M6" s="38">
+      <c r="K6" s="8" t="n"/>
+      <c r="M6" s="13">
         <f>Expenses!C10</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="20">
-      <c r="B8" s="30" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="C8" s="48" t="n"/>
-      <c r="D8" s="49" t="n"/>
-      <c r="F8" s="36" t="inlineStr">
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>TOTAL PROJECTS</t>
         </is>
       </c>
-      <c r="G8" s="48" t="n"/>
-      <c r="H8" s="49" t="n"/>
-      <c r="J8" s="43" t="inlineStr">
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>PAYMENTS RECEIVED</t>
         </is>
       </c>
-      <c r="K8" s="49" t="n"/>
-      <c r="M8" s="29" t="inlineStr">
+      <c r="K8" s="19" t="n"/>
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>SEND MONEY TOTAL</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="27.95" customHeight="1" s="20">
-      <c r="B9" s="35">
+    <row r="9" ht="28" customHeight="1">
+      <c r="B9" s="21">
         <f>F6-M6-M9</f>
         <v/>
       </c>
-      <c r="C9" s="48" t="n"/>
-      <c r="D9" s="49" t="n"/>
-      <c r="F9" s="33">
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="F9" s="22">
         <f>COUNTA(Projects!A3:A24)</f>
         <v/>
       </c>
-      <c r="G9" s="48" t="n"/>
-      <c r="H9" s="49" t="n"/>
-      <c r="J9" s="39">
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="J9" s="23">
         <f>COUNTIF(Projects!G3:G24, "Received")</f>
         <v/>
       </c>
-      <c r="K9" s="49" t="n"/>
-      <c r="M9" s="28">
+      <c r="K9" s="19" t="n"/>
+      <c r="M9" s="24">
         <f>'Send Money'!B12</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" s="20">
+    <row r="11" ht="24" customHeight="1">
       <c r="B11" s="25" t="inlineStr">
         <is>
           <t>NEW SPLIT — FROM 1 SEP 2026 (Company 30% · Shaista / Amara / Urooj 23.33% each)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" s="20">
-      <c r="B13" s="37" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>TOTAL REVENUE (PKR)</t>
         </is>
       </c>
-      <c r="C13" s="48" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>COMPANY SHARE (Total)</t>
         </is>
       </c>
-      <c r="G13" s="48" t="n"/>
-      <c r="H13" s="49" t="n"/>
-      <c r="J13" s="26" t="inlineStr">
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>TEAM SHARE (Total)</t>
         </is>
       </c>
-      <c r="K13" s="49" t="n"/>
-      <c r="M13" s="41" t="inlineStr">
+      <c r="K13" s="8" t="n"/>
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>TOTAL PURCHASES</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="27.95" customHeight="1" s="20">
-      <c r="B14" s="21">
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="10">
         <f>'Revenue Split'!B30</f>
         <v/>
       </c>
-      <c r="C14" s="48" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="F14" s="42">
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="F14" s="11">
         <f>'Revenue Split'!C30</f>
         <v/>
       </c>
-      <c r="G14" s="48" t="n"/>
-      <c r="H14" s="49" t="n"/>
-      <c r="J14" s="32">
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="J14" s="12">
         <f>SUM('Revenue Split'!D30:F30)</f>
         <v/>
       </c>
-      <c r="K14" s="49" t="n"/>
-      <c r="M14" s="38">
+      <c r="K14" s="8" t="n"/>
+      <c r="M14" s="13">
         <f>Expenses!C15</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" s="20">
-      <c r="B16" s="30" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>NET PROFIT</t>
         </is>
       </c>
-      <c r="C16" s="48" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="F16" s="36" t="inlineStr">
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>TOTAL PROJECTS</t>
         </is>
       </c>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="49" t="n"/>
-      <c r="J16" s="43" t="inlineStr">
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="n"/>
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>PAYMENTS RECEIVED</t>
         </is>
       </c>
-      <c r="K16" s="49" t="n"/>
-      <c r="M16" s="29" t="inlineStr">
+      <c r="K16" s="19" t="n"/>
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>SEND MONEY TOTAL</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="27.95" customHeight="1" s="20">
-      <c r="B17" s="35">
+    <row r="17" ht="28" customHeight="1">
+      <c r="B17" s="21">
         <f>F14-M14-M17</f>
         <v/>
       </c>
-      <c r="C17" s="48" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="F17" s="33">
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="F17" s="22">
         <f>COUNTA('Revenue Split'!A29:A29)</f>
         <v/>
       </c>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="49" t="n"/>
-      <c r="J17" s="39">
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="17" t="n"/>
+      <c r="J17" s="23">
         <f>COUNTIF('Revenue Split'!G29:G29, "Received")</f>
         <v/>
       </c>
-      <c r="K17" s="49" t="n"/>
-      <c r="M17" s="28">
+      <c r="K17" s="19" t="n"/>
+      <c r="M17" s="24">
         <f>'Send Money'!B16</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1" s="20">
+    <row r="19" ht="24" customHeight="1">
       <c r="B19" s="25" t="inlineStr">
         <is>
           <t>OVERALL SUMMARY (Old + New Combined)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" s="20">
-      <c r="B21" s="37" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>OVERALL REVENUE (PKR)</t>
         </is>
       </c>
-      <c r="C21" s="48" t="n"/>
-      <c r="D21" s="48" t="n"/>
-      <c r="E21" s="49" t="n"/>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>OVERALL NET PROFIT</t>
         </is>
       </c>
-      <c r="G21" s="48" t="n"/>
-      <c r="H21" s="49" t="n"/>
-      <c r="I21" s="36" t="inlineStr">
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>TOTAL PROJECTS</t>
         </is>
       </c>
-      <c r="J21" s="48" t="n"/>
-      <c r="K21" s="49" t="n"/>
-      <c r="L21" s="43" t="inlineStr">
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="17" t="n"/>
+      <c r="L21" s="18" t="inlineStr">
         <is>
           <t>PAYMENTS RECEIVED</t>
         </is>
       </c>
-      <c r="M21" s="49" t="n"/>
-    </row>
-    <row r="22" ht="27.95" customHeight="1" s="20">
-      <c r="B22" s="21">
+      <c r="M21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="B22" s="10">
         <f>B6+B14</f>
         <v/>
       </c>
-      <c r="C22" s="48" t="n"/>
-      <c r="D22" s="48" t="n"/>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="35">
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="21">
         <f>B9+B17</f>
         <v/>
       </c>
-      <c r="G22" s="48" t="n"/>
-      <c r="H22" s="49" t="n"/>
-      <c r="I22" s="33">
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="22">
         <f>F9+F17</f>
         <v/>
       </c>
-      <c r="J22" s="48" t="n"/>
-      <c r="K22" s="49" t="n"/>
-      <c r="L22" s="39">
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="17" t="n"/>
+      <c r="L22" s="23">
         <f>J9+J17</f>
         <v/>
       </c>
-      <c r="M22" s="49" t="n"/>
+      <c r="M22" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="44">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B11:M11"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="M17"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="B11:M11"/>
     <mergeCell ref="M8"/>
-    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="J14:K14"/>
+    <mergeCell ref="I22:K22"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="B13:D13"/>
@@ -1087,11 +995,10 @@
     <mergeCell ref="I21:K21"/>
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="F22:H22"/>
+    <mergeCell ref="J6:K6"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="B19:M19"/>
-    <mergeCell ref="J6:K6"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="J8:K8"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="M5"/>
@@ -1110,7 +1017,7 @@
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="M16"/>
     <mergeCell ref="M6"/>
-    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="J17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1123,1280 +1030,1240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="20" min="1" max="1"/>
-    <col width="16" customWidth="1" style="20" min="2" max="2"/>
-    <col width="22" customWidth="1" style="20" min="3" max="3"/>
-    <col width="14" customWidth="1" style="20" min="4" max="5"/>
-    <col width="10" customWidth="1" style="20" min="6" max="6"/>
-    <col width="14" customWidth="1" style="20" min="7" max="8"/>
-    <col width="18" customWidth="1" style="20" min="9" max="9"/>
-    <col width="14" customWidth="1" style="20" min="10" max="10"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>HEXALEVEL — CLIENT PROJECTS TRACKER</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" s="20">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Project Start</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Client Name</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>Service Type</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>Payment Status</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
         <is>
           <t>Payment Date</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="27" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="26" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" s="20">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Ranked Skill</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>Mortgage Leads flow</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="30" t="n">
         <v>25000</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>12-Jan-2026</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t>Meezan</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" s="20">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Crm +Wp</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="30" t="n">
         <v>15000</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>INR</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>20-Feb-2026</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>Payoneer</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" s="20">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>GHL all services</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="30" t="n">
         <v>350</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr"/>
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>Waiting for payment</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" s="20">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="J5" s="28" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Lahore</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Life insurance</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="30" t="n">
         <v>40000</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>21-Feb-2026</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
         <is>
           <t>HBL</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" s="20">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Mehroz</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>GHL Work</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="30" t="n">
         <v>28600</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
         <is>
           <t>3 Mar 2026</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
         <is>
           <t>Meezan</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" s="20">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Waleed</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Seo site</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>WP</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="30" t="n">
         <v>29000</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>25 Feb 2026</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" s="20">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Upwork</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Funnel designing</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="30" t="n">
         <v>9382</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
         <is>
           <t>15 Mar 2026</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J9" s="28" t="inlineStr">
         <is>
           <t>Meezan</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" s="20">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Crm +Wp</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="30" t="n">
         <v>15000</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>INR</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>20-Feb-2026</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
         <is>
           <t>Payoneer</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" s="20">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Mehroz</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>A2p</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="30" t="n">
         <v>19250</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
         <is>
           <t>27 Mar 2026</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
         <is>
           <t>Meezan</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" s="20">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>April 2026</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>haris</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="30" t="n">
         <v>46334</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>6 April 2026</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
         <is>
           <t>Payoneer</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" s="20">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>April 2026</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Mehroz</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>A2p</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="30" t="n">
         <v>33600</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>16 April 2026</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
         <is>
           <t>Meezan</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" s="20">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>April 2026</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>CRM+WP</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="30" t="n">
         <v>42199</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>24 April 2026</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
         <is>
           <t>Payoneer</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" s="20">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>April 2026</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Usa + Fiver</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="30" t="n">
         <v>80163</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>25 April 2026</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
         <is>
           <t>HBL</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" s="20">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Haris</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="30" t="n">
         <v>44401</v>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>3 May 2026</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
         <is>
           <t>Payoneer</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" s="20">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Usa</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="30" t="n">
         <v>85616</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
         <is>
           <t>15 May 2026</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" s="20">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Mehroz</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>A2P</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="30" t="n">
         <v>29400</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
         <is>
           <t>18 May 2026</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J18" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" s="20">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>June 2026</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Haris</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="30" t="n">
         <v>44614</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
         <is>
           <t>4 June 2026</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="I19" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
         <is>
           <t>Payoneer</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" s="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>shelim</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>WP</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>WP</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="30" t="n">
         <v>7000</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="inlineStr">
         <is>
           <t>20 June 2026</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="I20" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1" s="20">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Sheen</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="30" t="n">
         <v>15000</v>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="I21" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>Meezan</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" s="20">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>12/09/2026</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>Usa</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="30" t="n">
         <v>23113</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>12/09/2026</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="I22" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" s="20">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="30" t="n">
         <v>21920</v>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="I23" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20.1" customHeight="1" s="20">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>27/10/2026</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="30" t="n">
         <v>36099</v>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="inlineStr">
         <is>
           <t>27/10/2026</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="I24" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="45" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="50" t="n"/>
-      <c r="C25" s="50" t="n"/>
-      <c r="D25" s="51" t="n"/>
-      <c r="E25" s="8">
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="33">
         <f>SUM(E3:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="46" t="n"/>
-      <c r="G25" s="46" t="n"/>
-      <c r="H25" s="46" t="n"/>
-      <c r="I25" s="46" t="n"/>
-      <c r="J25" s="46" t="n"/>
-    </row>
-    <row r="26" ht="20.1" customHeight="1" s="20">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="32" t="n"/>
+      <c r="H25" s="32" t="n"/>
+      <c r="I25" s="32" t="n"/>
+      <c r="J25" s="32" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>19/10/26</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>Umair</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>GHL</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="30" t="n">
         <v>20000</v>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H26" s="28" t="inlineStr">
         <is>
           <t>19/10/26</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="I26" s="29" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J26" s="28" t="inlineStr">
         <is>
           <t>Meezan</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ghl</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2416,1072 +2283,1078 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="20" min="1" max="1"/>
-    <col width="14" customWidth="1" style="20" min="2" max="6"/>
-    <col width="12" customWidth="1" style="20" min="7" max="7"/>
-    <col width="14" customWidth="1" style="20" min="8" max="8"/>
-    <col width="12" customWidth="1" style="20" min="9" max="11"/>
-    <col width="14" customWidth="1" style="20" min="12" max="12"/>
-    <col width="18" customWidth="1" style="20" min="13" max="13"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>HEXALEVEL — REVENUE SPLIT  |  50% Company · 50% Team</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="21.95" customHeight="1" s="20">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Amount (PKR)</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>Company 50%</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="34" t="inlineStr">
         <is>
           <t>Team 50%</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>Date Received</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>Shaista</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
         <is>
           <t>Amara</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="26" t="inlineStr">
         <is>
           <t>Tax on Transfer</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.95" customHeight="1" s="20">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="19" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="35" t="n">
         <v>25000</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="35">
         <f>B3*0.5</f>
         <v/>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="35">
         <f>B3*0.5</f>
         <v/>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>26 Jan 2026</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="18.95" customHeight="1" s="20">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr"/>
+    </row>
+    <row r="4" ht="19" customHeight="1">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="35" t="n">
         <v>54541</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="35">
         <f>B4*0.5</f>
         <v/>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="35">
         <f>B4*0.5</f>
         <v/>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>20 Feb 2026</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" s="20">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr"/>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="35" t="n">
         <v>40000</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="35">
         <f>B5*0.5</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="35">
         <f>B5*0.5</f>
         <v/>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>21 Feb 2026</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>HBI</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="18.95" customHeight="1" s="20">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr"/>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="35" t="n">
         <v>29000</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="35">
         <f>B6*0.5</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="35">
         <f>B6*0.5</f>
         <v/>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>25 Feb 2026</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="18.95" customHeight="1" s="20">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr"/>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="35" t="n">
         <v>28600</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="35">
         <f>B7*0.5</f>
         <v/>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="35">
         <f>B7*0.5</f>
         <v/>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>3 Mar 2026</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="18.95" customHeight="1" s="20">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr"/>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="35" t="n">
         <v>9382</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="35">
         <f>B8*0.5</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="35">
         <f>B8*0.5</f>
         <v/>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>15 Mar 2026</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="18.95" customHeight="1" s="20">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr"/>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="35" t="n">
         <v>42671</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="35">
         <f>B9*0.5</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="35">
         <f>B9*0.5</f>
         <v/>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>25 Mar 2026</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="I9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="18.95" customHeight="1" s="20">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr"/>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="35" t="n">
         <v>19250</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="35">
         <f>B10*0.5</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="35">
         <f>B10*0.5</f>
         <v/>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>27 Mar 2026</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="18.95" customHeight="1" s="20">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="35" t="n">
         <v>46334</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="35">
         <f>B11*0.5</f>
         <v/>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="35">
         <f>B11*0.5</f>
         <v/>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>6 Apr 2026</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n"/>
-    </row>
-    <row r="12" ht="18.95" customHeight="1" s="20">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr"/>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="35" t="n">
         <v>33600</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="35">
         <f>B12*0.5</f>
         <v/>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="35">
         <f>B12*0.5</f>
         <v/>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>16 Apr 2026</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="18.95" customHeight="1" s="20">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr"/>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="35" t="n">
         <v>42199</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="35">
         <f>B13*0.5</f>
         <v/>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="35">
         <f>B13*0.5</f>
         <v/>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>24 Apr 2026</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="18.95" customHeight="1" s="20">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="I13" s="28" t="inlineStr"/>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="35" t="n">
         <v>80163</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="35">
         <f>B14*0.5</f>
         <v/>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="35">
         <f>B14*0.5</f>
         <v/>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>25 Apr 2026</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>Hbl</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="18.95" customHeight="1" s="20">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="35" t="n">
         <v>44401</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="35">
         <f>B15*0.5</f>
         <v/>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="35">
         <f>B15*0.5</f>
         <v/>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>4 May 2026</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="18.95" customHeight="1" s="20">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="I15" s="28" t="inlineStr"/>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="35" t="n">
         <v>85616</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="35">
         <f>B16*0.5</f>
         <v/>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="35">
         <f>B16*0.5</f>
         <v/>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>15 May 2026</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="18.95" customHeight="1" s="20">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="I16" s="28" t="inlineStr"/>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="35" t="n">
         <v>29400</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="35">
         <f>B17*0.5</f>
         <v/>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="35">
         <f>B17*0.5</f>
         <v/>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>18 May 2026</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" s="20">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="I17" s="28" t="inlineStr"/>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="35" t="n">
         <v>44614</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="35">
         <f>B18*0.5</f>
         <v/>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="35">
         <f>B18*0.5</f>
         <v/>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>4 Jun 2026</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I18" s="3" t="n"/>
-    </row>
-    <row r="19" ht="18.95" customHeight="1" s="20">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="I18" s="28" t="inlineStr"/>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="35" t="n">
         <v>7000</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="35">
         <f>B19*0.5</f>
         <v/>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="35">
         <f>B19*0.5</f>
         <v/>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>20 Jun 2026</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I19" s="3" t="n"/>
-    </row>
-    <row r="20" ht="18.95" customHeight="1" s="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="I19" s="28" t="inlineStr"/>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="35" t="n">
         <v>15000</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="35">
         <f>B20*0.5</f>
         <v/>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="35">
         <f>B20*0.5</f>
         <v/>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>12 Jul 2026</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I20" s="3" t="n"/>
-    </row>
-    <row r="21" ht="18.95" customHeight="1" s="20">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="I20" s="28" t="inlineStr"/>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="35" t="n">
         <v>23113</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="35">
         <f>B21*0.5</f>
         <v/>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="35">
         <f>B21*0.5</f>
         <v/>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>12 Sep 2026</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="28" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n"/>
-    </row>
-    <row r="22" ht="18.95" customHeight="1" s="20">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="I21" s="28" t="inlineStr"/>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="35" t="n">
         <v>21920</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="35">
         <f>B22*0.5</f>
         <v/>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="35">
         <f>B22*0.5</f>
         <v/>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>30 Sep 2026</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I22" s="3" t="n"/>
-    </row>
-    <row r="23" ht="18.95" customHeight="1" s="20">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="I22" s="28" t="inlineStr"/>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="35" t="n">
         <v>36099</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="35">
         <f>B23*0.5</f>
         <v/>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="35">
         <f>B23*0.5</f>
         <v/>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>27 Oct 2026</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>Askari</t>
         </is>
       </c>
-      <c r="I23" s="3" t="n"/>
+      <c r="I23" s="28" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="36">
         <f>SUM(B3:B23)</f>
         <v/>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="36">
         <f>SUM(C3:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="36">
         <f>SUM(D3:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-    </row>
-    <row r="27" ht="27.95" customHeight="1" s="20">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="37" t="n"/>
+      <c r="H24" s="37" t="n"/>
+      <c r="I24" s="37" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>HEXALEVEL — REVENUE SPLIT (NEW MODEL, effective 1 Sep 2026) | Company 30% · Shaista 23.33% · Amara 23.33% · Urooj 23.33%</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="21.95" customHeight="1" s="20">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="34" t="inlineStr">
         <is>
           <t>Amount (PKR)</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>Company 30%</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="34" t="inlineStr">
         <is>
           <t>Shaista 23.33%</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="34" t="inlineStr">
         <is>
           <t>Amara 23.33%</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="34" t="inlineStr">
         <is>
           <t>Urooj 23.33%</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr">
         <is>
           <t>Date Received</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="I28" s="26" t="inlineStr">
         <is>
           <t>Shaista</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>Amara</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>Urooj</t>
         </is>
       </c>
-      <c r="L28" s="1" t="inlineStr">
+      <c r="L28" s="26" t="inlineStr">
         <is>
           <t>Tax on Transfer</t>
         </is>
       </c>
-      <c r="M28" s="1" t="inlineStr">
+      <c r="M28" s="26" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18.95" customHeight="1" s="20">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="35" t="n">
         <v>20000</v>
       </c>
-      <c r="C29" s="10">
-        <f>B29*0.3</f>
-        <v/>
-      </c>
-      <c r="D29" s="10">
+      <c r="C29" s="35">
+        <f>B29*0.30</f>
+        <v/>
+      </c>
+      <c r="D29" s="35">
         <f>B29*(7/30)</f>
         <v/>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="35">
         <f>B29*(7/30)</f>
         <v/>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="35">
         <f>B29*(7/30)</f>
         <v/>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H29" s="28" t="inlineStr">
         <is>
           <t>19/10/26</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" s="28" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" s="28" t="inlineStr">
         <is>
           <t>Nayapay</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K29" s="28" t="inlineStr">
         <is>
           <t>UBL</t>
         </is>
       </c>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
+      <c r="L29" s="28" t="inlineStr"/>
+      <c r="M29" s="28" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="45" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="36">
         <f>SUM(B29:B29)</f>
         <v/>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="36">
         <f>SUM(C29:C29)</f>
         <v/>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="36">
         <f>SUM(D29:D29)</f>
         <v/>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="36">
         <f>SUM(E29:E29)</f>
         <v/>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="36">
         <f>SUM(F29:F29)</f>
         <v/>
       </c>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="G30" s="37" t="n"/>
+      <c r="H30" s="37" t="n"/>
+      <c r="I30" s="37" t="n"/>
+      <c r="J30" s="37" t="n"/>
+      <c r="K30" s="37" t="n"/>
+      <c r="L30" s="37" t="n"/>
+      <c r="M30" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3501,181 +3374,181 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="20" min="1" max="1"/>
-    <col width="24" customWidth="1" style="20" min="2" max="2"/>
-    <col width="18" customWidth="1" style="20" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PURCHASES — Items &amp; Prices</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="21.95" customHeight="1" s="20">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Item / Purchase</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Name / Link</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>Price (PKR)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.95" customHeight="1" s="20">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="19" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>theghlvideo.com</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="35" t="n">
         <v>3314.4</v>
       </c>
     </row>
-    <row r="4" ht="18.95" customHeight="1" s="20">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="19" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Upwork Connects</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>$15</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="35" t="n">
         <v>4830</v>
       </c>
     </row>
-    <row r="5" ht="18.95" customHeight="1" s="20">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Fiver Course</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Chain solution</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="35" t="n">
         <v>1999</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" s="20">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>6 course Leads generation</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>6/6 course</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="35" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" s="20">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Buy Crm</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Guarantee Crm</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="35" t="n">
         <v>370</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" s="20">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>BUY EMAIL THEGHLVIDEO</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="10" t="n">
+      <c r="B8" s="29" t="inlineStr"/>
+      <c r="C8" s="35" t="n">
         <v>2533.82</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" s="20">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Renew hexalevel Domain</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="10" t="n">
+      <c r="B9" s="29" t="inlineStr"/>
+      <c r="C9" s="35" t="n">
         <v>4955</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="11">
+      <c r="B10" s="37" t="inlineStr"/>
+      <c r="C10" s="36">
         <f>SUM(C3:C9)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="27.95" customHeight="1" s="20">
-      <c r="A12" s="19" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>NEW PURCHASES — Items &amp; Prices (from 1 Sep 2026, split 3 ways)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="21.95" customHeight="1" s="20">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Item / Purchase</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Name / Link</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>Price (PKR)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18.95" customHeight="1" s="20">
-      <c r="A14" s="14" t="n"/>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="39" t="inlineStr"/>
+      <c r="B14" s="39" t="inlineStr"/>
+      <c r="C14" s="39" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="11">
+      <c r="B15" s="37" t="inlineStr"/>
+      <c r="C15" s="36">
         <f>SUM(C14:C14)</f>
         <v/>
       </c>
@@ -3698,120 +3571,120 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="20" min="1" max="1"/>
-    <col width="20" customWidth="1" style="20" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SEND MONEY — Payments Made</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="21.95" customHeight="1" s="20">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Send Money To</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Amount Sent (PKR)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.95" customHeight="1" s="20">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="19" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Send Sundas for email testing</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="35" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="4" ht="18.95" customHeight="1" s="20">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="19" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Meeting Fiver with Ahsan</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="35" t="n">
         <v>10000</v>
       </c>
     </row>
-    <row r="5" ht="18.95" customHeight="1" s="20">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Waqar Udhar</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="35" t="n">
         <v>3250</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" s="20">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
-    </row>
-    <row r="7" ht="18.95" customHeight="1" s="20">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
-    </row>
-    <row r="8" ht="18.95" customHeight="1" s="20">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
-    </row>
-    <row r="9" ht="18.95" customHeight="1" s="20">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="15" t="n"/>
-    </row>
-    <row r="10" ht="18.95" customHeight="1" s="20">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="18.95" customHeight="1" s="20">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="40" t="inlineStr"/>
+      <c r="B6" s="40" t="inlineStr"/>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="40" t="inlineStr"/>
+      <c r="B7" s="40" t="inlineStr"/>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="40" t="inlineStr"/>
+      <c r="B8" s="40" t="inlineStr"/>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="40" t="inlineStr"/>
+      <c r="B9" s="40" t="inlineStr"/>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="40" t="inlineStr"/>
+      <c r="B10" s="40" t="inlineStr"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="40" t="inlineStr"/>
+      <c r="B11" s="40" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="36">
         <f>SUM(B3:B11)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="27.95" customHeight="1" s="20">
-      <c r="A14" s="19" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>NEW SEND MONEY — Payments Made (from 1 Sep 2026, split 3 ways)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="21.95" customHeight="1" s="20">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Send Money To</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Amount Sent (PKR)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="36">
         <f>SUM(B15:B15)</f>
         <v/>
       </c>
@@ -3831,412 +3704,375 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="20" min="1" max="1"/>
-    <col width="24" customWidth="1" style="20" min="2" max="2"/>
-    <col width="16" customWidth="1" style="20" min="3" max="3"/>
-    <col width="14" customWidth="1" style="20" min="4" max="4"/>
-    <col width="16" customWidth="1" style="20" min="5" max="7"/>
-    <col width="20" customWidth="1" style="20" min="8" max="9"/>
-    <col width="26" customWidth="1" style="20" min="10" max="10"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>HEXALEVEL — SCENARIO C (3 REGISTERED MEMBERS · 2 WORKING · 1 SKIPPED)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20.1" customHeight="1" s="20">
-      <c r="A2" s="47" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>Rule: Skipped member gets 0 direct share. Unallocated share (23.33%) goes to Company (53.33%). In Net Profit, surplus is credited ONLY to working members.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" s="20">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Project ID</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Client Name</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>Amount (PKR)</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>Shaista (23.33%)</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="34" t="inlineStr">
         <is>
           <t>Amara (23.33%)</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="34" t="inlineStr">
         <is>
           <t>Urooj (23.33%)</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="34" t="inlineStr">
         <is>
           <t>Skipped Share to Co (23.33%)</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="34" t="inlineStr">
         <is>
           <t>Total Co Share (53.33%)</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="26" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" s="20">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>PRJ-023</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Umair (All 3 Active)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="35" t="n">
         <v>20000</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n">
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="n">
         <v>4666.67</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="35" t="n">
         <v>4666.67</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="35" t="n">
         <v>4666.67</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" s="35" t="n">
         <v>6000</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="29" t="inlineStr">
         <is>
           <t>Scenario B (All 3 Active)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" s="20">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>PRJ-024</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Demo Client A</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="35" t="n">
         <v>50000</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n">
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="n">
         <v>11666.67</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="35" t="n">
         <v>11666.67</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="35" t="n">
         <v>11666.67</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="35" t="n">
         <v>26666.67</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="29" t="inlineStr">
         <is>
           <t>Urooj Skipped -&gt; Surplus to Co</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" s="20">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>PRJ-025</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Demo Client B</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="35" t="n">
         <v>30000</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n">
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="n">
         <v>7000</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="35" t="n">
         <v>7000</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="35" t="n">
         <v>7000</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="35" t="n">
         <v>16000</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="29" t="inlineStr">
         <is>
           <t>Amara Skipped -&gt; Surplus to Co</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="11">
+      <c r="B7" s="37" t="inlineStr"/>
+      <c r="C7" s="36">
         <f>SUM(C4:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="11">
+      <c r="D7" s="37" t="inlineStr"/>
+      <c r="E7" s="36">
         <f>SUM(E4:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="36">
         <f>SUM(F4:F6)</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="36">
         <f>SUM(G4:G6)</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="36">
         <f>SUM(H4:H6)</f>
         <v/>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="36">
         <f>SUM(I4:I6)</f>
         <v/>
       </c>
-      <c r="J7" s="12" t="n"/>
-    </row>
-    <row r="10" ht="26.1" customHeight="1" s="20">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="J7" s="37" t="inlineStr"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>PARTNER NET PROFIT STATEMENTS (Including Scenario C Attribution)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="21.95" customHeight="1" s="20">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Partner Name</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Direct Project Payouts</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>Scenario C Surplus Credit</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>Company Net Distribution</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="34" t="inlineStr">
         <is>
           <t>Total Deductions</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="34" t="inlineStr">
         <is>
           <t>Final Net Profit</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" s="20">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>Shaista (Co-Founder)</t>
         </is>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="35">
         <f>SUM('Revenue Split'!D3:D23)*0.5 + E7</f>
         <v/>
       </c>
-      <c r="C12" s="10">
-        <f>H4*0.5 + H5*1</f>
-        <v/>
-      </c>
-      <c r="D12" s="10">
+      <c r="C12" s="35">
+        <f>H4*0.5 + H5*1.0</f>
+        <v/>
+      </c>
+      <c r="D12" s="35">
         <f>('Revenue Split'!C24 + 'Revenue Split'!C30 - Expenses!C10 - Expenses!C15 - 'Send Money'!B12)/3</f>
         <v/>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="43">
         <f>B12+C12+D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="44" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" s="20">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Amara (Co-Founder)</t>
         </is>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="35">
         <f>SUM('Revenue Split'!D3:D23)*0.5 + F7</f>
         <v/>
       </c>
-      <c r="C13" s="10">
-        <f>H4*0.5 + H6*1</f>
-        <v/>
-      </c>
-      <c r="D13" s="10">
+      <c r="C13" s="35">
+        <f>H4*0.5 + H6*1.0</f>
+        <v/>
+      </c>
+      <c r="D13" s="35">
         <f>('Revenue Split'!C24 + 'Revenue Split'!C30 - Expenses!C10 - Expenses!C15 - 'Send Money'!B12)/3</f>
         <v/>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="43">
         <f>B13+C13+D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="44" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" s="20">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>Urooj (Partner)</t>
         </is>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="35">
         <f>G7</f>
         <v/>
       </c>
-      <c r="C14" s="10">
-        <f>H6*1</f>
-        <v/>
-      </c>
-      <c r="D14" s="10">
+      <c r="C14" s="35">
+        <f>H6*1.0</f>
+        <v/>
+      </c>
+      <c r="D14" s="35">
         <f>('Revenue Split'!C24 + 'Revenue Split'!C30 - Expenses!C10 - Expenses!C15 - 'Send Money'!B12)/3</f>
         <v/>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="43">
         <f>B14+C14+D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G14" s="44" t="inlineStr">
         <is>
           <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PRJ-015</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1050</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2400</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Scenario C: Amara &amp; Urooj (2 Working)</t>
         </is>
       </c>
     </row>
